--- a/BWI/bestwine_output/bestwine_Maldives.xlsx
+++ b/BWI/bestwine_output/bestwine_Maldives.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1618,6 +1618,184 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>The Yeoman Group</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The Yeoman Group</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>9560</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6a Finiunimaage</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20072</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yeoman-group.com</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>info@yeoman-group.com</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>+960 332-0212</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/yeoman-group-maldives/</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Marco Ingrassia</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Brand Ambassador</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-ingrassia-8624041a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>The Yeoman Group</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>The Yeoman Group</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9560</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6a Finiunimaage</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20072</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yeoman-group.com</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>info@yeoman-group.com</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>+960 332-0212</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/yeoman-group-maldives/</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Aminath Hasna</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aminath-hasna-b147aa258/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Maldives.xlsx
+++ b/BWI/bestwine_output/bestwine_Maldives.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1796,6 +1796,75 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Vintners Maldives</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>168249</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Malé</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>H. Sikkage Aage</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20079</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vintnersmaldives.com</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>info@vintnersmaldives.com</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Hiroko Kataoka</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
